--- a/data/Diessenhofen/investment_decision/Willisdorf_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Willisdorf_SFH_2005-2014_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92390377899246</v>
+        <v>3.201146556548897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>4035.231585003035</v>
       </c>
       <c r="F3" t="n">
-        <v>16.63196916140963</v>
+        <v>3.201146556548897</v>
       </c>
       <c r="G3" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="H3" t="n">
-        <v>15.65062922434098</v>
+        <v>3.201146556548897</v>
       </c>
       <c r="I3" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="J3" t="n">
-        <v>15.65062922434098</v>
+        <v>3.201146556548897</v>
       </c>
       <c r="K3" t="n">
         <v>4035.231585003035</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>16.92390377899246</v>
+        <v>19.49704479158379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>4035.231585003035</v>
       </c>
       <c r="F4" t="n">
-        <v>16.63196916140963</v>
+        <v>19.84186179827096</v>
       </c>
       <c r="G4" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="H4" t="n">
-        <v>15.65062922434098</v>
+        <v>19.71707934865582</v>
       </c>
       <c r="I4" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="J4" t="n">
-        <v>15.65062922434098</v>
+        <v>20.03312901069989</v>
       </c>
       <c r="K4" t="n">
         <v>4035.231585003035</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>18.29850273658232</v>
+        <v>25.50158416806949</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>4035.231585003035</v>
       </c>
       <c r="F5" t="n">
-        <v>18.231149767628</v>
+        <v>25.5015841680695</v>
       </c>
       <c r="G5" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="H5" t="n">
-        <v>15.65062922434098</v>
+        <v>25.50158416806951</v>
       </c>
       <c r="I5" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="J5" t="n">
-        <v>16.77464330993633</v>
+        <v>25.11478406598456</v>
       </c>
       <c r="K5" t="n">
         <v>4035.231585003035</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>18.29850273658232</v>
+        <v>25.5015841680694</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>4035.231585003035</v>
       </c>
       <c r="F6" t="n">
-        <v>18.231149767628</v>
+        <v>25.5015841680695</v>
       </c>
       <c r="G6" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="H6" t="n">
-        <v>16.77464330993633</v>
+        <v>25.50158416806951</v>
       </c>
       <c r="I6" t="n">
         <v>4035.231585003035</v>
       </c>
       <c r="J6" t="n">
-        <v>16.77464330993633</v>
+        <v>25.11478406598456</v>
       </c>
       <c r="K6" t="n">
         <v>4035.231585003035</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3.534271466663734</v>
+        <v>5.115166742007371</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.534271466663734</v>
+        <v>5.115166742007371</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.690916877663619</v>
+        <v>6.789184766499142</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.690916877663619</v>
+        <v>6.789184766499142</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5.19600830312443</v>
+        <v>7.52020582290631</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.19600830312443</v>
+        <v>7.52020582290631</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.458536418380365</v>
+        <v>7.900163926483078</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.458536418380365</v>
+        <v>7.900163926483078</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6.052847377504552</v>
+        <v>8.760312808988765</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.611618979040772</v>
+        <v>8.121720994313698</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5.611618979040772</v>
+        <v>8.121720994313698</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0007665641788235295</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0007665641788235295</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0007665641788235295</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0008255306541176471</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0007665641788235295</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001238295981176471</v>
+        <v>0.0007665641788235295</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001297262456470588</v>
+        <v>0.0008255306541176471</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001297262456470588</v>
+        <v>0.0008255306541176471</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001238295981176471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470588</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001249854977365011</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001244901224536872</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470588</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470588</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470589</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001244901224536872</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470588</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001297262456470589</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001592094832941177</v>
+        <v>0.001244901224536871</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.1929802800651918</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1897980667195923</v>
       </c>
       <c r="G19" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.1619152767547198</v>
       </c>
       <c r="I19" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1560891172320083</v>
       </c>
       <c r="K19" t="n">
         <v>1.052551584</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.1929802800651918</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.1897980667195923</v>
       </c>
       <c r="G20" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.1619152767547198</v>
       </c>
       <c r="I20" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1560891172320083</v>
       </c>
       <c r="K20" t="n">
         <v>1.052551584</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.1929802800651918</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.1897980667195923</v>
       </c>
       <c r="G21" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.1619152767547198</v>
       </c>
       <c r="I21" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.1560891172320083</v>
       </c>
       <c r="K21" t="n">
         <v>1.052551584</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.03132593999999999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.03058158637511739</v>
       </c>
       <c r="G29" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.05651116327483865</v>
       </c>
       <c r="I29" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.05914284446478702</v>
       </c>
       <c r="K29" t="n">
         <v>1.052551584</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.03132593999999999</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.03058158637511739</v>
       </c>
       <c r="G30" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.05651116327483865</v>
       </c>
       <c r="I30" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.05914284446478702</v>
       </c>
       <c r="K30" t="n">
         <v>1.052551584</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.03132593999999999</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>1.052551584</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.03132594000000082</v>
       </c>
       <c r="G31" t="n">
         <v>1.052551584</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.05651116327483865</v>
       </c>
       <c r="I31" t="n">
         <v>1.052551584</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.05914284446478702</v>
       </c>
       <c r="K31" t="n">
         <v>1.052551584</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.435037548404578</v>
+        <v>1.244528774576154</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F54" t="n">
-        <v>1.377568283749568</v>
+        <v>1.229787155752625</v>
       </c>
       <c r="G54" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H54" t="n">
-        <v>1.355921079255406</v>
+        <v>1.237385140541586</v>
       </c>
       <c r="I54" t="n">
         <v>4.218453561035802</v>
       </c>
       <c r="J54" t="n">
-        <v>1.424688302615811</v>
+        <v>1.228995835837347</v>
       </c>
       <c r="K54" t="n">
         <v>4.218453561035802</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.435037548404578</v>
+        <v>1.460803932406475</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F55" t="n">
-        <v>1.377568283749568</v>
+        <v>1.401916686432631</v>
       </c>
       <c r="G55" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H55" t="n">
-        <v>1.355921079255406</v>
+        <v>1.461347204494391</v>
       </c>
       <c r="I55" t="n">
         <v>4.660064140312916</v>
       </c>
       <c r="J55" t="n">
-        <v>1.424688302615811</v>
+        <v>1.351383628244021</v>
       </c>
       <c r="K55" t="n">
         <v>4.660064140312916</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.435037548404578</v>
+        <v>1.460803932406475</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F56" t="n">
-        <v>1.377568283749568</v>
+        <v>1.401916686432631</v>
       </c>
       <c r="G56" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H56" t="n">
-        <v>1.355921079255406</v>
+        <v>1.461347204494406</v>
       </c>
       <c r="I56" t="n">
         <v>4.961233795020703</v>
       </c>
       <c r="J56" t="n">
-        <v>1.424688302615811</v>
+        <v>1.351383628244021</v>
       </c>
       <c r="K56" t="n">
         <v>4.961233795020703</v>
@@ -2734,13 +2734,13 @@
         <v>6.95935537226388</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5676519167955456</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="I62" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5676519167955456</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="K62" t="n">
         <v>6.95935537226388</v>
@@ -2765,19 +2765,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5740916510069314</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="G63" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5957388555010927</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="I63" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5957388555010931</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="K63" t="n">
         <v>6.95935537226388</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.132614368390968</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F64" t="n">
-        <v>1.196523367257363</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="G64" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H64" t="n">
-        <v>1.239817776245687</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="I64" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="J64" t="n">
-        <v>1.171050552885281</v>
+        <v>0.5676519167955454</v>
       </c>
       <c r="K64" t="n">
         <v>6.95935537226388</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.10229233256178</v>
+        <v>0.1951848276973079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F65" t="n">
-        <v>1.161247324473135</v>
+        <v>0.2540720736711515</v>
       </c>
       <c r="G65" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H65" t="n">
-        <v>1.239817776245687</v>
+        <v>0.1946415556093761</v>
       </c>
       <c r="I65" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="J65" t="n">
-        <v>1.14625612452656</v>
+        <v>0.3176954398431907</v>
       </c>
       <c r="K65" t="n">
         <v>6.95935537226388</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.10229233256178</v>
+        <v>0.1951848276973079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>6.95935537226388</v>
       </c>
       <c r="F66" t="n">
-        <v>1.161247324473135</v>
+        <v>0.2540720736711515</v>
       </c>
       <c r="G66" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="H66" t="n">
-        <v>1.215023347886966</v>
+        <v>0.1946415556093761</v>
       </c>
       <c r="I66" t="n">
         <v>6.95935537226388</v>
       </c>
       <c r="J66" t="n">
-        <v>1.14625612452656</v>
+        <v>0.3176954398431907</v>
       </c>
       <c r="K66" t="n">
         <v>6.95935537226388</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2772445652050773</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2772445652050773</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4748978183709233</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4748978183709233</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6308457061522857</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6308457061522857</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7604756421935006</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7604756421935006</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8716440145608046</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.8716440145608046</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2772445652050773</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2772445652050773</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4748978183709233</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4748978183709233</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6308457061522857</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6308457061522857</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7604756421935006</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7604756421935006</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8716440145608046</v>
+        <v>6.95935537226388</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8716440145608046</v>
+        <v>6.95935537226388</v>
       </c>
     </row>
     <row r="82">
